--- a/datosIntentosSin0PValues.xlsx
+++ b/datosIntentosSin0PValues.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
           <t>Num errores por tiempo excedido</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -580,6 +590,12 @@
       <c r="S2" t="n">
         <v>0.6510540771590529</v>
       </c>
+      <c r="T2" t="n">
+        <v>0.7181031901915098</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.7181031901915135</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -641,6 +657,12 @@
       <c r="S3" t="n">
         <v>0.07141295494398167</v>
       </c>
+      <c r="T3" t="n">
+        <v>0.636108787044283</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.636108787044283</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -702,6 +724,12 @@
       <c r="S4" t="n">
         <v>0.0777132202655708</v>
       </c>
+      <c r="T4" t="n">
+        <v>0.8514711820709451</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.8514711820709451</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -763,6 +791,12 @@
       <c r="S5" t="n">
         <v>1.086144364090511e-08</v>
       </c>
+      <c r="T5" t="n">
+        <v>0.02522599200881579</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.02522599200881579</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -824,6 +858,12 @@
       <c r="S6" t="n">
         <v>1.54308054809054e-34</v>
       </c>
+      <c r="T6" t="n">
+        <v>6.134579909629005e-86</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6.134579909630115e-86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -885,6 +925,12 @@
       <c r="S7" t="n">
         <v>0.6939439162789298</v>
       </c>
+      <c r="T7" t="n">
+        <v>0.2696218145254221</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.2696218145254216</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -946,6 +992,12 @@
       <c r="S8" t="n">
         <v>0.06520207566710867</v>
       </c>
+      <c r="T8" t="n">
+        <v>1.329258771372718e-22</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.329258771372718e-22</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1007,6 +1059,12 @@
       <c r="S9" t="n">
         <v>0.01390449326001688</v>
       </c>
+      <c r="T9" t="n">
+        <v>4.684818337377445e-60</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4.684818337377445e-60</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1068,6 +1126,12 @@
       <c r="S10" t="n">
         <v>0.3882676398133627</v>
       </c>
+      <c r="T10" t="n">
+        <v>0.0134336456772232</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.01343364567722296</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1129,6 +1193,12 @@
       <c r="S11" t="n">
         <v>0.06532872971865232</v>
       </c>
+      <c r="T11" t="n">
+        <v>6.710405263358274e-12</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6.710405263358041e-12</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1190,6 +1260,12 @@
       <c r="S12" t="n">
         <v>2.464033197108536e-09</v>
       </c>
+      <c r="T12" t="n">
+        <v>3.13213341622317e-20</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.13213341622317e-20</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1251,6 +1327,12 @@
       <c r="S13" t="n">
         <v>0.348103313316989</v>
       </c>
+      <c r="T13" t="n">
+        <v>0.880640401013522</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.8806404010135174</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1312,6 +1394,12 @@
       <c r="S14" t="n">
         <v>0.1854493795166698</v>
       </c>
+      <c r="T14" t="n">
+        <v>1.522825919511393e-17</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.522825919511393e-17</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1373,6 +1461,12 @@
       <c r="S15" t="n">
         <v>0.7657791835094623</v>
       </c>
+      <c r="T15" t="n">
+        <v>1.266920520826787e-40</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.266920520826964e-40</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1434,6 +1528,12 @@
       <c r="S16" t="n">
         <v>0.06821943520283033</v>
       </c>
+      <c r="T16" t="n">
+        <v>5.775449255870415e-07</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.775449255870263e-07</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1495,6 +1595,12 @@
       <c r="S17" t="n">
         <v>0.0003816759411597951</v>
       </c>
+      <c r="T17" t="n">
+        <v>8.517420935305335e-05</v>
+      </c>
+      <c r="U17" t="n">
+        <v>8.517420935305335e-05</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1556,6 +1662,12 @@
       <c r="S18" t="n">
         <v>6.58162786992835e-196</v>
       </c>
+      <c r="T18" t="n">
+        <v>0.2852589291628081</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.2852589291628081</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1615,6 +1727,146 @@
         <v>6.58162786992835e-196</v>
       </c>
       <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.001071054482415451</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.001071054482415451</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.7181031901915098</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.636108787044283</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8514711820709451</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.02522599200881579</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.134579909629005e-86</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2696218145254221</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.329258771372718e-22</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.684818337377445e-60</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.0134336456772232</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.710405263358274e-12</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.13213341622317e-20</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.880640401013522</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.522825919511393e-17</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.266920520826787e-40</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5.775449255870415e-07</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>8.517420935305335e-05</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2852589291628081</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.001071054482415451</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.7181031901915135</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.636108787044283</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8514711820709451</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.02522599200881579</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.134579909630115e-86</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.2696218145254216</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.329258771372718e-22</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.684818337377445e-60</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.01343364567722296</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.710405263358041e-12</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.13213341622317e-20</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.8806404010135174</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.522825919511393e-17</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.266920520826964e-40</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5.775449255870263e-07</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8.517420935305335e-05</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2852589291628081</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.001071054482415451</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
         <v>0</v>
       </c>
     </row>
